--- a/Project_ETF/ETF_Investment_Portfolio/0052/ETF_Investment_Portfolio_20260715.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/0052/ETF_Investment_Portfolio_20260715.xlsx
@@ -1107,17 +1107,17 @@
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>2449</t>
+          <t>3665</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>京元電子</t>
+          <t>貿聯-KY</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>1,905,321</t>
+          <t>313,672</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
@@ -1129,17 +1129,17 @@
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>3665</t>
+          <t>2449</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>貿聯-KY</t>
+          <t>京元電子</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>313,672</t>
+          <t>1,905,321</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
@@ -1217,17 +1217,17 @@
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>3653</t>
+          <t>3189</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>健策</t>
+          <t>景碩</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>152,499</t>
+          <t>577,000</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
@@ -1239,17 +1239,17 @@
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>3189</t>
+          <t>3653</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>景碩</t>
+          <t>健策</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>577,000</t>
+          <t>152,499</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
@@ -1261,17 +1261,17 @@
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>3034</t>
+          <t>2337</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>聯詠</t>
+          <t>旺宏</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>1,000,822</t>
+          <t>3,219,000</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
@@ -1283,17 +1283,17 @@
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>2337</t>
+          <t>3034</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>旺宏</t>
+          <t>聯詠</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>3,219,000</t>
+          <t>1,000,822</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
@@ -1327,17 +1327,17 @@
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
         <is>
-          <t>2395</t>
+          <t>6770</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>研華</t>
+          <t>力積電</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>807,897</t>
+          <t>5,710,000</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr">
@@ -1349,17 +1349,17 @@
     <row r="55">
       <c r="A55" s="3" t="inlineStr">
         <is>
-          <t>6770</t>
+          <t>2395</t>
         </is>
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>力積電</t>
+          <t>研華</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>5,710,000</t>
+          <t>807,897</t>
         </is>
       </c>
       <c r="D55" s="4" t="inlineStr">
@@ -1415,17 +1415,17 @@
     <row r="58">
       <c r="A58" s="3" t="inlineStr">
         <is>
-          <t>3044</t>
+          <t>2376</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>健鼎</t>
+          <t>技嘉</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>768,000</t>
+          <t>935,659</t>
         </is>
       </c>
       <c r="D58" s="4" t="inlineStr">
@@ -1437,17 +1437,17 @@
     <row r="59">
       <c r="A59" s="3" t="inlineStr">
         <is>
-          <t>2376</t>
+          <t>3044</t>
         </is>
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
-          <t>技嘉</t>
+          <t>健鼎</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>935,659</t>
+          <t>768,000</t>
         </is>
       </c>
       <c r="D59" s="4" t="inlineStr">
@@ -1569,17 +1569,17 @@
     <row r="65">
       <c r="A65" s="3" t="inlineStr">
         <is>
-          <t>3036</t>
+          <t>2356</t>
         </is>
       </c>
       <c r="B65" s="3" t="inlineStr">
         <is>
-          <t>文曄</t>
+          <t>英業達</t>
         </is>
       </c>
       <c r="C65" s="4" t="inlineStr">
         <is>
-          <t>1,377,384</t>
+          <t>4,448,578</t>
         </is>
       </c>
       <c r="D65" s="4" t="inlineStr">
@@ -1591,17 +1591,17 @@
     <row r="66">
       <c r="A66" s="3" t="inlineStr">
         <is>
-          <t>2356</t>
+          <t>3036</t>
         </is>
       </c>
       <c r="B66" s="3" t="inlineStr">
         <is>
-          <t>英業達</t>
+          <t>文曄</t>
         </is>
       </c>
       <c r="C66" s="4" t="inlineStr">
         <is>
-          <t>4,448,578</t>
+          <t>1,377,384</t>
         </is>
       </c>
       <c r="D66" s="4" t="inlineStr">
@@ -1635,17 +1635,17 @@
     <row r="68">
       <c r="A68" s="3" t="inlineStr">
         <is>
-          <t>202608WVHFQ6F</t>
+          <t>6257</t>
         </is>
       </c>
       <c r="B68" s="3" t="inlineStr">
         <is>
-          <t>富邦科技ETF期貨</t>
+          <t>矽格</t>
         </is>
       </c>
       <c r="C68" s="4" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>775,000</t>
         </is>
       </c>
       <c r="D68" s="4" t="inlineStr">
@@ -1657,17 +1657,17 @@
     <row r="69">
       <c r="A69" s="3" t="inlineStr">
         <is>
-          <t>2347</t>
+          <t>202608WVHFQ6F</t>
         </is>
       </c>
       <c r="B69" s="3" t="inlineStr">
         <is>
-          <t>聯強</t>
+          <t>富邦科技ETF期貨</t>
         </is>
       </c>
       <c r="C69" s="4" t="inlineStr">
         <is>
-          <t>2,188,107</t>
+          <t>300</t>
         </is>
       </c>
       <c r="D69" s="4" t="inlineStr">
@@ -1679,17 +1679,17 @@
     <row r="70">
       <c r="A70" s="3" t="inlineStr">
         <is>
-          <t>2492</t>
+          <t>2347</t>
         </is>
       </c>
       <c r="B70" s="3" t="inlineStr">
         <is>
-          <t>華新科</t>
+          <t>聯強</t>
         </is>
       </c>
       <c r="C70" s="4" t="inlineStr">
         <is>
-          <t>497,000</t>
+          <t>2,188,107</t>
         </is>
       </c>
       <c r="D70" s="4" t="inlineStr">
@@ -1723,17 +1723,17 @@
     <row r="72">
       <c r="A72" s="3" t="inlineStr">
         <is>
-          <t>6257</t>
+          <t>2492</t>
         </is>
       </c>
       <c r="B72" s="3" t="inlineStr">
         <is>
-          <t>矽格</t>
+          <t>華新科</t>
         </is>
       </c>
       <c r="C72" s="4" t="inlineStr">
         <is>
-          <t>775,000</t>
+          <t>497,000</t>
         </is>
       </c>
       <c r="D72" s="4" t="inlineStr">
@@ -1789,17 +1789,17 @@
     <row r="75">
       <c r="A75" s="3" t="inlineStr">
         <is>
-          <t>2353</t>
+          <t>5434</t>
         </is>
       </c>
       <c r="B75" s="3" t="inlineStr">
         <is>
-          <t>宏碁</t>
+          <t>崇越</t>
         </is>
       </c>
       <c r="C75" s="4" t="inlineStr">
         <is>
-          <t>4,954,956</t>
+          <t>290,000</t>
         </is>
       </c>
       <c r="D75" s="4" t="inlineStr">
@@ -1811,17 +1811,17 @@
     <row r="76">
       <c r="A76" s="3" t="inlineStr">
         <is>
-          <t>5434</t>
+          <t>2353</t>
         </is>
       </c>
       <c r="B76" s="3" t="inlineStr">
         <is>
-          <t>崇越</t>
+          <t>宏碁</t>
         </is>
       </c>
       <c r="C76" s="4" t="inlineStr">
         <is>
-          <t>290,000</t>
+          <t>4,954,956</t>
         </is>
       </c>
       <c r="D76" s="4" t="inlineStr">
@@ -1965,17 +1965,17 @@
     <row r="83">
       <c r="A83" s="3" t="inlineStr">
         <is>
-          <t>2455</t>
+          <t>6789</t>
         </is>
       </c>
       <c r="B83" s="3" t="inlineStr">
         <is>
-          <t>全新</t>
+          <t>采鈺</t>
         </is>
       </c>
       <c r="C83" s="4" t="inlineStr">
         <is>
-          <t>319,000</t>
+          <t>178,000</t>
         </is>
       </c>
       <c r="D83" s="4" t="inlineStr">
@@ -1987,17 +1987,17 @@
     <row r="84">
       <c r="A84" s="3" t="inlineStr">
         <is>
-          <t>2467</t>
+          <t>6196</t>
         </is>
       </c>
       <c r="B84" s="3" t="inlineStr">
         <is>
-          <t>志聖</t>
+          <t>帆宣</t>
         </is>
       </c>
       <c r="C84" s="4" t="inlineStr">
         <is>
-          <t>156,000</t>
+          <t>170,000</t>
         </is>
       </c>
       <c r="D84" s="4" t="inlineStr">
@@ -2031,17 +2031,17 @@
     <row r="86">
       <c r="A86" s="3" t="inlineStr">
         <is>
-          <t>6196</t>
+          <t>5269</t>
         </is>
       </c>
       <c r="B86" s="3" t="inlineStr">
         <is>
-          <t>帆宣</t>
+          <t>祥碩</t>
         </is>
       </c>
       <c r="C86" s="4" t="inlineStr">
         <is>
-          <t>170,000</t>
+          <t>65,538</t>
         </is>
       </c>
       <c r="D86" s="4" t="inlineStr">
@@ -2053,17 +2053,17 @@
     <row r="87">
       <c r="A87" s="3" t="inlineStr">
         <is>
-          <t>5269</t>
+          <t>2455</t>
         </is>
       </c>
       <c r="B87" s="3" t="inlineStr">
         <is>
-          <t>祥碩</t>
+          <t>全新</t>
         </is>
       </c>
       <c r="C87" s="4" t="inlineStr">
         <is>
-          <t>65,538</t>
+          <t>319,000</t>
         </is>
       </c>
       <c r="D87" s="4" t="inlineStr">
@@ -2075,17 +2075,17 @@
     <row r="88">
       <c r="A88" s="3" t="inlineStr">
         <is>
-          <t>6789</t>
+          <t>2467</t>
         </is>
       </c>
       <c r="B88" s="3" t="inlineStr">
         <is>
-          <t>采鈺</t>
+          <t>志聖</t>
         </is>
       </c>
       <c r="C88" s="4" t="inlineStr">
         <is>
-          <t>178,000</t>
+          <t>156,000</t>
         </is>
       </c>
       <c r="D88" s="4" t="inlineStr">
@@ -2097,17 +2097,17 @@
     <row r="89">
       <c r="A89" s="3" t="inlineStr">
         <is>
-          <t>3030</t>
+          <t>2451</t>
         </is>
       </c>
       <c r="B89" s="3" t="inlineStr">
         <is>
-          <t>德律</t>
+          <t>創見</t>
         </is>
       </c>
       <c r="C89" s="4" t="inlineStr">
         <is>
-          <t>254,000</t>
+          <t>331,000</t>
         </is>
       </c>
       <c r="D89" s="4" t="inlineStr">
@@ -2141,17 +2141,17 @@
     <row r="91">
       <c r="A91" s="3" t="inlineStr">
         <is>
-          <t>2451</t>
+          <t>3030</t>
         </is>
       </c>
       <c r="B91" s="3" t="inlineStr">
         <is>
-          <t>創見</t>
+          <t>德律</t>
         </is>
       </c>
       <c r="C91" s="4" t="inlineStr">
         <is>
-          <t>331,000</t>
+          <t>254,000</t>
         </is>
       </c>
       <c r="D91" s="4" t="inlineStr">
@@ -2163,17 +2163,17 @@
     <row r="92">
       <c r="A92" s="3" t="inlineStr">
         <is>
-          <t>3532</t>
+          <t>4919</t>
         </is>
       </c>
       <c r="B92" s="3" t="inlineStr">
         <is>
-          <t>台勝科</t>
+          <t>新唐</t>
         </is>
       </c>
       <c r="C92" s="4" t="inlineStr">
         <is>
-          <t>114,000</t>
+          <t>335,000</t>
         </is>
       </c>
       <c r="D92" s="4" t="inlineStr">
@@ -2185,17 +2185,17 @@
     <row r="93">
       <c r="A93" s="3" t="inlineStr">
         <is>
-          <t>4919</t>
+          <t>3532</t>
         </is>
       </c>
       <c r="B93" s="3" t="inlineStr">
         <is>
-          <t>新唐</t>
+          <t>台勝科</t>
         </is>
       </c>
       <c r="C93" s="4" t="inlineStr">
         <is>
-          <t>335,000</t>
+          <t>114,000</t>
         </is>
       </c>
       <c r="D93" s="4" t="inlineStr">
